--- a/model/Output_Budget/5. Prosumer percentage/Base Cases/0/Output_0_40.xlsx
+++ b/model/Output_Budget/5. Prosumer percentage/Base Cases/0/Output_0_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2904358.099031371</v>
+        <v>2904358.09903137</v>
       </c>
     </row>
     <row r="7">
@@ -26261,19 +26261,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>996991.2386902553</v>
+        <v>996991.2386902552</v>
       </c>
       <c r="C2" t="n">
-        <v>996991.2386902553</v>
+        <v>996991.2386902552</v>
       </c>
       <c r="D2" t="n">
-        <v>996991.2386902553</v>
+        <v>996991.2386902552</v>
       </c>
       <c r="E2" t="n">
         <v>983231.6413739761</v>
       </c>
       <c r="F2" t="n">
-        <v>991470.6169539343</v>
+        <v>991470.6169539342</v>
       </c>
       <c r="G2" t="n">
         <v>992122.1605309875</v>
@@ -26288,7 +26288,7 @@
         <v>983231.6413739761</v>
       </c>
       <c r="K2" t="n">
-        <v>991470.6169539343</v>
+        <v>991470.6169539342</v>
       </c>
       <c r="L2" t="n">
         <v>992592.0492026102</v>
@@ -26303,7 +26303,7 @@
         <v>988129.8611110091</v>
       </c>
       <c r="P2" t="n">
-        <v>967336.5726469889</v>
+        <v>967336.5726469888</v>
       </c>
     </row>
     <row r="3">
@@ -26365,13 +26365,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>569049.7736743363</v>
+        <v>569049.7736743361</v>
       </c>
       <c r="C4" t="n">
-        <v>569049.7736743363</v>
+        <v>569049.7736743361</v>
       </c>
       <c r="D4" t="n">
-        <v>569049.7736743363</v>
+        <v>569049.7736743361</v>
       </c>
       <c r="E4" t="n">
         <v>561196.2485531277</v>
@@ -26395,13 +26395,13 @@
         <v>565898.7845505781</v>
       </c>
       <c r="L4" t="n">
-        <v>566538.8611556027</v>
+        <v>566538.8611556028</v>
       </c>
       <c r="M4" t="n">
-        <v>566538.8611556027</v>
+        <v>566538.8611556028</v>
       </c>
       <c r="N4" t="n">
-        <v>566538.8611556027</v>
+        <v>566538.8611556028</v>
       </c>
       <c r="O4" t="n">
         <v>563991.9911079244</v>
@@ -26478,40 +26478,40 @@
         <v>394313.8650159191</v>
       </c>
       <c r="E6" t="n">
-        <v>102668.3432907246</v>
+        <v>102668.3432907244</v>
       </c>
       <c r="F6" t="n">
-        <v>385034.9227278868</v>
+        <v>385034.9227278866</v>
       </c>
       <c r="G6" t="n">
-        <v>393487.4321340104</v>
+        <v>393487.4321340103</v>
       </c>
       <c r="H6" t="n">
-        <v>394417.2907373137</v>
+        <v>394417.2907373136</v>
       </c>
       <c r="I6" t="n">
-        <v>394417.2907373137</v>
+        <v>394417.2907373136</v>
       </c>
       <c r="J6" t="n">
-        <v>112798.621302133</v>
+        <v>112798.6213021328</v>
       </c>
       <c r="K6" t="n">
-        <v>375834.5033197817</v>
+        <v>375834.5033197816</v>
       </c>
       <c r="L6" t="n">
-        <v>391786.7736569914</v>
+        <v>391786.7736569913</v>
       </c>
       <c r="M6" t="n">
-        <v>394526.5050366035</v>
+        <v>394526.5050366034</v>
       </c>
       <c r="N6" t="n">
-        <v>394526.5050366035</v>
+        <v>394526.5050366034</v>
       </c>
       <c r="O6" t="n">
-        <v>119866.7728230279</v>
+        <v>119866.7728230277</v>
       </c>
       <c r="P6" t="n">
-        <v>386201.9260478141</v>
+        <v>386201.9260478139</v>
       </c>
     </row>
   </sheetData>
